--- a/artfynd/S 1414-2026 artfynd.xlsx
+++ b/artfynd/S 1414-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98421</v>
+        <v>98424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
